--- a/education_surveys/023_life_saving_attitudes_survey--education_surveys.xlsx
+++ b/education_surveys/023_life_saving_attitudes_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cpr_training_is_not_available</t>
+          <t>first_aid_training_programs_are_not_available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CPR training is not available</t>
+          <t>First Aid training programs are not available</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_safety_programs_choices</t>
+          <t>first_aid_confidence_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_aid_training_programs_are_not_available</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>First Aid training programs are not available</t>
+          <t>Very confident</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>very_confident</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Very confident</t>
+          <t>Somewhat confident</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>somewhat_confident</t>
+          <t>not_confident_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Somewhat confident</t>
+          <t>Not confident at all</t>
         </is>
       </c>
     </row>
@@ -1146,216 +1146,216 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_confident_at_all</t>
+          <t>not_confident</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not confident at all</t>
+          <t>Not confident</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_aid_confidence_choices</t>
+          <t>cpr_confidence_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>somewhat_confident</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Somewhat confident</t>
+          <t>Very confident</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_aid_confidence_choices</t>
+          <t>cpr_confidence_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>very_confident</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Very confident</t>
+          <t>Somewhat confident</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>first_aid_confidence_choices</t>
+          <t>cpr_confidence_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_confident</t>
+          <t>not_confident_at_all</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Not confident</t>
+          <t>Not confident at all</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cpr_confidence_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>very_confident</t>
+          <t>first_aid_training</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Very confident</t>
+          <t>First aid training</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cpr_confidence_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>somewhat_confident</t>
+          <t>cpr_training</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Somewhat confident</t>
+          <t>CPR training</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cpr_confidence_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_confident_at_all</t>
+          <t>first_aid_and_cpr_training</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Not confident at all</t>
+          <t>First aid and CPR training</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cpr_confidence_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>somewhat_confident</t>
+          <t>neither_first_aid_nor_cpr_training</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Somewhat confident</t>
+          <t>Neither first aid nor CPR training</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cpr_confidence_choices</t>
+          <t>school_support_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>very_confident</t>
+          <t>school_nurse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Very confident</t>
+          <t>School nurse</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>school_support_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_aid_training</t>
+          <t>school_security</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>First aid training</t>
+          <t>School security</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>school_support_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cpr_training</t>
+          <t>school_janitor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CPR training</t>
+          <t>School janitor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>school_support_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>first_aid_and_cpr_training</t>
+          <t>school_principal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>First aid and CPR training</t>
+          <t>School principal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>school_support_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>neither_first_aid_nor_cpr_training</t>
+          <t>school_district</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Neither first aid nor CPR training</t>
+          <t>School district</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>school_nurse</t>
+          <t>school_administration</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>School nurse</t>
+          <t>School administration</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>school_security</t>
+          <t>school_teachers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>School security</t>
+          <t>School teachers</t>
         </is>
       </c>
     </row>
@@ -1401,386 +1401,386 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>school_janitor</t>
+          <t>school_students</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>School janitor</t>
+          <t>School students</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>school_support_choices</t>
+          <t>first_aid_kits_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>school_principal</t>
+          <t>first_aid_kits</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>School principal</t>
+          <t>First Aid kits</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>school_support_choices</t>
+          <t>first_aid_kits_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>school_district</t>
+          <t>automated_external_defibrillators_(aeds)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>School district</t>
+          <t>Automated External Defibrillators (AEDs)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>school_support_choices</t>
+          <t>first_aid_kits_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>school_administration</t>
+          <t>both_first_aid_kits_and_aeds</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>School administration</t>
+          <t>Both first aid kits and AEDs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>school_support_choices</t>
+          <t>first_aid_kits_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>school_teachers</t>
+          <t>neither_first_aid_kits_nor_aeds</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>School teachers</t>
+          <t>Neither first aid kits nor AEDs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>school_support_choices</t>
+          <t>cpr_equipment_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>school_students</t>
+          <t>cpr_equipment</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>School students</t>
+          <t>CPR equipment</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>first_aid_kits_choices</t>
+          <t>cpr_equipment_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>first_aid_kits</t>
+          <t>aeds</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>First Aid kits</t>
+          <t>AEDs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>first_aid_kits_choices</t>
+          <t>cpr_equipment_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>automated_external_defibrillators_(aeds)</t>
+          <t>both_cpr_equipment_and_aeds</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Automated External Defibrillators (AEDs)</t>
+          <t>Both CPR equipment and AEDs</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>first_aid_kits_choices</t>
+          <t>cpr_equipment_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>both_first_aid_kits_and_aeds</t>
+          <t>neither_cpr_equipment_nor_aeds</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Both first aid kits and AEDs</t>
+          <t>Neither CPR equipment nor AEDs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>first_aid_kits_choices</t>
+          <t>cpr_procedures_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>neither_first_aid_kits_nor_aeds</t>
+          <t>adult_cpr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Neither first aid kits nor AEDs</t>
+          <t>Adult CPR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cpr_equipment_choices</t>
+          <t>cpr_procedures_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cpr_equipment</t>
+          <t>child_cpr</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CPR equipment</t>
+          <t>Child CPR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cpr_equipment_choices</t>
+          <t>cpr_procedures_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>aeds</t>
+          <t>infant_cpr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AEDs</t>
+          <t>Infant CPR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cpr_equipment_choices</t>
+          <t>cpr_procedures_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>both_cpr_equipment_and_aeds</t>
+          <t>all_of_the_above</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Both CPR equipment and AEDs</t>
+          <t>All of the above</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cpr_equipment_choices</t>
+          <t>cpr_procedures_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>neither_cpr_equipment_nor_aeds</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Neither CPR equipment nor AEDs</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cpr_procedures_choices</t>
+          <t>emergency_plan_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>adult_cpr</t>
+          <t>emergency_plan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Adult CPR</t>
+          <t>Emergency Plan</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cpr_procedures_choices</t>
+          <t>emergency_plan_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>child_cpr</t>
+          <t>automated_external_defibrillator_(aed)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Child CPR</t>
+          <t>Automated External Defibrillator (AED)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cpr_procedures_choices</t>
+          <t>emergency_plan_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>infant_cpr</t>
+          <t>both_emergency_plan_and_aed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Infant CPR</t>
+          <t>Both emergency plan and AED</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cpr_procedures_choices</t>
+          <t>emergency_plan_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>all_of_the_above</t>
+          <t>neither_emergency_plan_nor_aed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Neither emergency plan nor AED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cpr_procedures_choices</t>
+          <t>training_location_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Schools</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>emergency_plan_choices</t>
+          <t>training_location_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>emergency_plan</t>
+          <t>workplace</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Emergency Plan</t>
+          <t>Workplace</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>emergency_plan_choices</t>
+          <t>training_location_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>automated_external_defibrillator_(aed)</t>
+          <t>community_centers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Automated External Defibrillator (AED)</t>
+          <t>Community centers</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>emergency_plan_choices</t>
+          <t>training_location_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>both_emergency_plan_and_aed</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Both emergency plan and AED</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>emergency_plan_choices</t>
+          <t>training_location_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>neither_emergency_plan_nor_aed</t>
+          <t>workplace_or_schools</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Neither emergency plan nor AED</t>
+          <t>Workplace or schools</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>schools_or_community_centers</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Schools or community centers</t>
         </is>
       </c>
     </row>
@@ -1809,97 +1809,97 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>workplace</t>
+          <t>all_of_the_above</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Workplace</t>
+          <t>All of the above</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>training_location_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>community_centers</t>
+          <t>in_the_school_office</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Community centers</t>
+          <t>In the school office</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>training_location_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>in_the_school_nurse's_office</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>In the school nurse's office</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>training_location_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>workplace_or_schools</t>
+          <t>in_the_school_gym</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Workplace or schools</t>
+          <t>In the school gym</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>training_location_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>schools_or_community_centers</t>
+          <t>in_the_school_cafeteria</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Schools or community centers</t>
+          <t>In the school cafeteria</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>training_location_choices</t>
+          <t>first_aid_kit_location_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>all_of_the_above</t>
+          <t>in_other_locations_within_the_school</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>In other locations within the school</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>in_the_school_office</t>
+          <t>in_the_school_parking_lot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>In the school office</t>
+          <t>In the school parking lot</t>
         </is>
       </c>
     </row>
@@ -1928,97 +1928,97 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>in_the_school_nurse's_office</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>In the school nurse's office</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>first_aid_kit_location_choices</t>
+          <t>cpr_certification_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>in_the_school_gym</t>
+          <t>cpr_certification_is_not_available</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>In the school gym</t>
+          <t>CPR certification is not available</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>first_aid_kit_location_choices</t>
+          <t>cpr_certification_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>in_the_school_cafeteria</t>
+          <t>basic_cpr_certification_is_not_available</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>In the school cafeteria</t>
+          <t>Basic CPR certification is not available</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>first_aid_kit_location_choices</t>
+          <t>cpr_certification_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>in_other_locations_within_the_school</t>
+          <t>advanced_cpr_certification_is_not_available</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>In other locations within the school</t>
+          <t>Advanced CPR certification is not available</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>first_aid_kit_location_choices</t>
+          <t>cpr_certification_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>in_the_school_parking_lot</t>
+          <t>cpr_certification_is_available</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>In the school parking lot</t>
+          <t>CPR certification is available</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>first_aid_kit_location_choices</t>
+          <t>cpr_certification_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>basic_cpr_certification_is_available</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Basic CPR certification is available</t>
         </is>
       </c>
     </row>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>cpr_certification_is_not_available</t>
+          <t>advanced_cpr_certification_is_available</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CPR certification is not available</t>
+          <t>Advanced CPR certification is available</t>
         </is>
       </c>
     </row>
@@ -2047,97 +2047,97 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>basic_cpr_certification_is_not_available</t>
+          <t>both_basic_and_advanced_cpr_certification_is_available</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Basic CPR certification is not available</t>
+          <t>Both basic and advanced CPR certification is available</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cpr_certification_choices</t>
+          <t>school_id_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>advanced_cpr_certification_is_not_available</t>
+          <t>001</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Advanced CPR certification is not available</t>
+          <t>001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cpr_certification_choices</t>
+          <t>school_id_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>cpr_certification_is_available</t>
+          <t>002</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CPR certification is available</t>
+          <t>002</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cpr_certification_choices</t>
+          <t>school_id_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>basic_cpr_certification_is_available</t>
+          <t>003</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Basic CPR certification is available</t>
+          <t>003</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cpr_certification_choices</t>
+          <t>school_id_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>advanced_cpr_certification_is_available</t>
+          <t>004</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Advanced CPR certification is available</t>
+          <t>004</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cpr_certification_choices</t>
+          <t>school_id_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>both_basic_and_advanced_cpr_certification_is_available</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Both basic and advanced CPR certification is available</t>
+          <t>005</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>006</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>007</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>008</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>009</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>009</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>010</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>010</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>011</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>011</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>012</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>013</t>
         </is>
       </c>
     </row>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>014</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>014</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>015</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>016</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>016</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>017</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>018</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>018</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>019</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>020</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>020</t>
         </is>
       </c>
     </row>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>021</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>022</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>022</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>023</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>023</t>
         </is>
       </c>
     </row>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>024</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>024</t>
         </is>
       </c>
     </row>
@@ -2472,95 +2472,10 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
-        <is>
-          <t>020</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>school_id_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>021</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>school_id_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>022</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>022</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>school_id_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>023</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>023</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>school_id_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>024</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>024</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>school_id_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
         <is>
           <t>025</t>
         </is>
